--- a/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,35</t>
+          <t>1,35; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,66</t>
+          <t>4,15; 14,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,89</t>
+          <t>4,29; 13,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 16,12</t>
+          <t>6,36; 16,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 31,13</t>
+          <t>10,06; 28,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,19</t>
+          <t>0,89; 4,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,95</t>
+          <t>6,4; 13,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 21,02</t>
+          <t>8,47; 20,53</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,61</t>
+          <t>3,84; 12,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 21,16</t>
+          <t>8,97; 21,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,68</t>
+          <t>1,29; 8,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 13,54</t>
+          <t>5,05; 14,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,01</t>
+          <t>5,98; 18,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,42</t>
+          <t>1,07; 5,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,33</t>
+          <t>5,18; 11,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 17,6</t>
+          <t>8,62; 17,46</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,07</t>
+          <t>1,37; 8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,39</t>
+          <t>3,09; 14,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 29,81</t>
+          <t>11,83; 30,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,0</t>
+          <t>0,99; 8,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 19,86</t>
+          <t>6,9; 19,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 24,78</t>
+          <t>6,62; 26,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,0</t>
+          <t>1,64; 6,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,01</t>
+          <t>5,88; 15,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 23,22</t>
+          <t>10,8; 23,32</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,67</t>
+          <t>1,36; 5,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 19,72</t>
+          <t>12,06; 20,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 24,25</t>
+          <t>9,11; 24,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,57</t>
+          <t>2,95; 8,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 20,74</t>
+          <t>12,33; 20,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 16,46</t>
+          <t>8,56; 16,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,16</t>
+          <t>2,77; 6,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,87</t>
+          <t>13,3; 18,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,02</t>
+          <t>9,98; 18,54</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,88</t>
+          <t>3,84; 10,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 20,68</t>
+          <t>10,99; 20,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 22,3</t>
+          <t>10,83; 22,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,87</t>
+          <t>2,02; 8,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,69; 23,14</t>
+          <t>12,96; 23,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 21,61</t>
+          <t>10,29; 22,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,28</t>
+          <t>3,65; 8,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 20,36</t>
+          <t>13,31; 20,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 19,71</t>
+          <t>11,92; 20,22</t>
         </is>
       </c>
     </row>
@@ -1225,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,89</t>
+          <t>0,0; 13,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 28,03</t>
+          <t>11,54; 28,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 18,2</t>
+          <t>3,36; 17,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,3; 31,19</t>
+          <t>13,43; 30,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 22,39</t>
+          <t>6,13; 21,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,78</t>
+          <t>0,48; 6,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,19; 26,17</t>
+          <t>15,03; 26,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 17,02</t>
+          <t>6,16; 17,15</t>
         </is>
       </c>
     </row>
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,27</t>
+          <t>2,82; 5,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,01</t>
+          <t>10,8; 14,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,85</t>
+          <t>11,05; 17,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,2</t>
+          <t>2,68; 5,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,51; 17,02</t>
+          <t>12,36; 16,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,92</t>
+          <t>11,22; 16,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,67</t>
+          <t>2,99; 4,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,23; 15,28</t>
+          <t>12,34; 15,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,96</t>
+          <t>11,7; 15,92</t>
         </is>
       </c>
     </row>
@@ -1402,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6677</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22983</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16917</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>31272</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1210; 7894</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3445; 11697</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4486; 14065</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3582</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6298; 16019</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13613; 38538</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1600; 8971</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11658; 24033</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20304; 49211</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13222</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9828</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10481</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4874</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17586</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>23703</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4334</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4012; 12962</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8489; 19941</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1251; 7781</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5655; 16157</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5712; 17496</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2025; 9562</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11223; 24032</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16409; 33227</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8631</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6339</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13452</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18911</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1177; 6947</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1909; 8988</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6135; 15745</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>860; 7299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5163; 14887</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4227; 16705</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11446</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8038; 20507</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12491; 26986</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35101</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32712</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33515</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26359</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18737</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>68616</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>59071</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2794; 11712</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26961; 45531</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19846; 53165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6718; 18949</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>25737; 42524</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18679; 36790</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11991; 26923</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>57514; 82100</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>43541; 80834</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9777</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20613</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18663</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6248</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25136</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25034</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16025</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>45748</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43697</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5660; 15971</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14897; 27757</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12937; 26804</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2842; 11348</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18461; 33501</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16733; 36149</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10516; 23639</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>36982; 55879</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>33623; 57041</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>26071</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>14644</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 7338</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7051; 17283</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2317; 11919</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2487</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9106; 20880</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4411; 15540</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>615; 7876</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>19379; 34139</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8685; 24165</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>85794</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>89175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26674</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>102596</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>102123</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>52682</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>188391</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>191298</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>19021; 35772</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>72291; 99409</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>72615; 112835</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19203; 36954</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>87144; 118822</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>83856; 125885</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>41610; 66286</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>169589; 210215</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>164388; 223602</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,78</t>
+          <t>1,23; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 14,08</t>
+          <t>4,41; 13,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,46</t>
+          <t>4,23; 13,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,17</t>
+          <t>6,15; 16,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 28,49</t>
+          <t>9,96; 32,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,99</t>
+          <t>0,95; 4,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,2</t>
+          <t>6,14; 13,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 20,53</t>
+          <t>8,36; 20,73</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,41</t>
+          <t>4,23; 13,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 21,06</t>
+          <t>8,89; 20,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,04</t>
+          <t>1,43; 8,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 14,42</t>
+          <t>4,88; 13,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,31</t>
+          <t>5,79; 18,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,05</t>
+          <t>1,09; 5,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,1</t>
+          <t>5,54; 11,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 17,46</t>
+          <t>8,91; 17,72</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,06</t>
+          <t>1,33; 7,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,53</t>
+          <t>2,63; 14,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 30,36</t>
+          <t>12,22; 31,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,4</t>
+          <t>0,99; 8,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 19,91</t>
+          <t>6,82; 20,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 26,16</t>
+          <t>7,14; 25,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,61</t>
+          <t>1,75; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 15,01</t>
+          <t>5,68; 14,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 23,32</t>
+          <t>10,98; 24,06</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,68</t>
+          <t>1,57; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,36</t>
+          <t>12,0; 19,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 24,41</t>
+          <t>8,76; 22,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,33</t>
+          <t>3,44; 8,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,33; 20,37</t>
+          <t>12,04; 20,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 16,86</t>
+          <t>8,27; 16,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,21</t>
+          <t>2,88; 6,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,3; 18,99</t>
+          <t>13,31; 19,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 18,54</t>
+          <t>9,85; 18,34</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,82</t>
+          <t>3,64; 10,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 20,48</t>
+          <t>10,4; 20,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 22,44</t>
+          <t>10,83; 21,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,08</t>
+          <t>2,07; 7,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,96; 23,52</t>
+          <t>13,07; 24,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 22,23</t>
+          <t>10,24; 22,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,21</t>
+          <t>3,37; 8,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 20,1</t>
+          <t>12,94; 19,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 20,22</t>
+          <t>11,87; 20,0</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,79</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,54; 28,29</t>
+          <t>11,23; 27,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 17,3</t>
+          <t>3,76; 19,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 30,78</t>
+          <t>13,73; 30,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 21,58</t>
+          <t>6,28; 21,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,19</t>
+          <t>0,48; 6,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,03; 26,48</t>
+          <t>14,64; 26,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 17,15</t>
+          <t>6,1; 16,79</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,3</t>
+          <t>2,78; 5,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 14,85</t>
+          <t>10,99; 15,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,05; 17,17</t>
+          <t>11,02; 17,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,17</t>
+          <t>2,75; 5,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 16,86</t>
+          <t>12,25; 16,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,84</t>
+          <t>10,91; 16,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,77</t>
+          <t>3,02; 4,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,34; 15,29</t>
+          <t>12,29; 15,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 15,92</t>
+          <t>11,84; 15,89</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1210; 7894</t>
+          <t>1106; 7829</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3445; 11697</t>
+          <t>3662; 11591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4486; 14065</t>
+          <t>4419; 14065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 3584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6298; 16019</t>
+          <t>6093; 16391</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13613; 38538</t>
+          <t>13477; 43403</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1600; 8971</t>
+          <t>1701; 8767</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11658; 24033</t>
+          <t>11191; 24468</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20304; 49211</t>
+          <t>20039; 49687</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>0; 4303</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4012; 12962</t>
+          <t>4415; 13702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8489; 19941</t>
+          <t>8418; 19292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1251; 7781</t>
+          <t>1385; 8346</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5655; 16157</t>
+          <t>5467; 15512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5712; 17496</t>
+          <t>5529; 17464</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2025; 9562</t>
+          <t>2060; 9845</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11223; 24032</t>
+          <t>12002; 25228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16409; 33227</t>
+          <t>16945; 33708</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1177; 6947</t>
+          <t>1146; 6389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1909; 8988</t>
+          <t>1626; 8659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6135; 15745</t>
+          <t>6338; 16145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>860; 7299</t>
+          <t>858; 7608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5163; 14887</t>
+          <t>5099; 15434</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4227; 16705</t>
+          <t>4557; 16407</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2840; 11446</t>
+          <t>3035; 11688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8038; 20507</t>
+          <t>7764; 20445</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12491; 26986</t>
+          <t>12701; 27840</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2794; 11712</t>
+          <t>3230; 11528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26961; 45531</t>
+          <t>26826; 43974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19846; 53165</t>
+          <t>19092; 50027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6718; 18949</t>
+          <t>7825; 19459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25737; 42524</t>
+          <t>25131; 43750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18679; 36790</t>
+          <t>18048; 36678</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11991; 26923</t>
+          <t>12484; 27392</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57514; 82100</t>
+          <t>57544; 84286</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43541; 80834</t>
+          <t>42974; 79973</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5660; 15971</t>
+          <t>5376; 15686</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14897; 27757</t>
+          <t>14098; 27545</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12937; 26804</t>
+          <t>12940; 25985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2842; 11348</t>
+          <t>2907; 11119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18461; 33501</t>
+          <t>18609; 34241</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16733; 36149</t>
+          <t>16647; 35824</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10516; 23639</t>
+          <t>9707; 23292</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36982; 55879</t>
+          <t>35961; 55397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33623; 57041</t>
+          <t>33476; 56396</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7338</t>
+          <t>0; 6474</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7051; 17283</t>
+          <t>6860; 16512</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2317; 11919</t>
+          <t>2592; 13579</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2487</t>
+          <t>0; 3091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9106; 20880</t>
+          <t>9314; 20906</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4411; 15540</t>
+          <t>4524; 15792</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>615; 7876</t>
+          <t>607; 8126</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19379; 34139</t>
+          <t>18877; 33773</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8685; 24165</t>
+          <t>8591; 23664</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19021; 35772</t>
+          <t>18811; 36281</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>72291; 99409</t>
+          <t>73572; 100484</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72615; 112835</t>
+          <t>72427; 112454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19203; 36954</t>
+          <t>19669; 36274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>87144; 118822</t>
+          <t>86351; 117902</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83856; 125885</t>
+          <t>81579; 123317</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41610; 66286</t>
+          <t>41958; 65636</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>169589; 210215</t>
+          <t>168896; 208998</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>164388; 223602</t>
+          <t>166358; 223191</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,7</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 13,95</t>
+          <t>6,06; 16,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 13,46</t>
+          <t>7,09; 18,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>1,42; 8,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,55</t>
+          <t>4,35; 14,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 32,09</t>
+          <t>4,44; 13,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,88</t>
+          <t>0,87; 5,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,43</t>
+          <t>6,41; 12,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 20,73</t>
+          <t>6,82; 13,88</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>1,28; 7,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 13,12</t>
+          <t>4,94; 13,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 20,38</t>
+          <t>6,07; 18,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,62</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,84</t>
+          <t>4,03; 12,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 18,27</t>
+          <t>8,69; 21,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,2</t>
+          <t>1,18; 5,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,65</t>
+          <t>5,29; 11,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 17,72</t>
+          <t>8,61; 17,77</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,42</t>
+          <t>0,99; 9,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,0</t>
+          <t>6,74; 19,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 31,13</t>
+          <t>5,29; 19,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,76</t>
+          <t>1,31; 8,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 20,64</t>
+          <t>2,62; 14,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 25,7</t>
+          <t>10,98; 28,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,75</t>
+          <t>1,73; 7,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 14,96</t>
+          <t>6,12; 15,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 24,06</t>
+          <t>10,03; 21,59</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,7%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,59</t>
+          <t>3,23; 8,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 19,67</t>
+          <t>11,96; 20,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 22,97</t>
+          <t>8,27; 16,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,55</t>
+          <t>1,48; 5,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,04; 20,96</t>
+          <t>12,23; 19,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 16,8</t>
+          <t>8,59; 17,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,32</t>
+          <t>2,84; 6,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 19,5</t>
+          <t>13,13; 18,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,34</t>
+          <t>9,45; 14,89</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>15,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,63</t>
+          <t>2,16; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,32</t>
+          <t>12,69; 23,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 21,76</t>
+          <t>9,26; 19,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,92</t>
+          <t>3,65; 10,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 24,04</t>
+          <t>10,62; 20,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 22,03</t>
+          <t>10,28; 21,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,09</t>
+          <t>3,6; 8,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,93</t>
+          <t>13,35; 20,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,0</t>
+          <t>11,08; 18,51</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>18,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,03</t>
+          <t>14,3; 31,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,76; 19,71</t>
+          <t>6,15; 22,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 12,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,73; 30,82</t>
+          <t>11,71; 28,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 21,93</t>
+          <t>2,48; 11,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,39</t>
+          <t>0,48; 5,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,64; 26,2</t>
+          <t>15,19; 26,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,79</t>
+          <t>5,27; 14,31</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,37</t>
+          <t>2,66; 5,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,99; 15,01</t>
+          <t>12,51; 17,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,02; 17,11</t>
+          <t>9,93; 14,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,07</t>
+          <t>2,72; 5,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,73</t>
+          <t>10,88; 15,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,91; 16,5</t>
+          <t>10,29; 14,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,72</t>
+          <t>2,96; 4,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 15,21</t>
+          <t>12,23; 15,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 15,89</t>
+          <t>10,77; 14,11</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14071</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3441</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>6677</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>22065</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1106; 7829</t>
+          <t>0; 3209</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3662; 11591</t>
+          <t>6000; 15966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4419; 14065</t>
+          <t>8580; 22090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3584</t>
+          <t>1277; 7511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6093; 16391</t>
+          <t>3612; 12179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13477; 43403</t>
+          <t>4575; 14178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1701; 8767</t>
+          <t>1565; 9319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11191; 24468</t>
+          <t>11679; 23589</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20039; 49687</t>
+          <t>15279; 31088</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7758</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13222</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3508</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9828</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23696</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4303</t>
+          <t>1243; 7432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4415; 13702</t>
+          <t>5536; 15179</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8418; 19292</t>
+          <t>5551; 16939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1385; 8346</t>
+          <t>0; 4734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5467; 15512</t>
+          <t>4204; 13165</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5529; 17464</t>
+          <t>8387; 20555</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2060; 9845</t>
+          <t>2226; 10252</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12002; 25228</t>
+          <t>11460; 24523</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16945; 33708</t>
+          <t>16178; 33406</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>3090</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4246</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10280</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9206</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>16549</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1146; 6389</t>
+          <t>861; 7816</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1626; 8659</t>
+          <t>5037; 14851</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6338; 16145</t>
+          <t>3011; 11168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>858; 7608</t>
+          <t>1130; 6951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5099; 15434</t>
+          <t>1619; 8899</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4557; 16407</t>
+          <t>5871; 15478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3035; 11688</t>
+          <t>2995; 12106</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7764; 20445</t>
+          <t>8368; 20510</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12701; 27840</t>
+          <t>11074; 23840</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12438</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33515</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24454</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6299</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32712</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12438</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33515</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>46463</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3230; 11528</t>
+          <t>7343; 19500</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26826; 43974</t>
+          <t>24962; 43293</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19092; 50027</t>
+          <t>16697; 33275</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7825; 19459</t>
+          <t>3055; 11693</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25131; 43750</t>
+          <t>27350; 44100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18048; 36678</t>
+          <t>15335; 30360</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12484; 27392</t>
+          <t>12296; 26712</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57544; 84286</t>
+          <t>56745; 81565</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42974; 79973</t>
+          <t>35957; 56664</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6248</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25136</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>9777</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>20613</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18663</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6248</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25136</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>39137</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5376; 15686</t>
+          <t>3027; 11050</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14098; 27545</t>
+          <t>18070; 32960</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12940; 25985</t>
+          <t>13730; 28831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2907; 11119</t>
+          <t>5379; 16047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18609; 34241</t>
+          <t>14400; 28022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16647; 35824</t>
+          <t>12202; 26026</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9707; 23292</t>
+          <t>10379; 23852</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35961; 55397</t>
+          <t>37104; 56599</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33476; 56396</t>
+          <t>29585; 49422</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11399</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>12604</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6474</t>
+          <t>0; 3383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6860; 16512</t>
+          <t>9696; 21153</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2592; 13579</t>
+          <t>4199; 15599</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3091</t>
+          <t>0; 6861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9314; 20906</t>
+          <t>7151; 17125</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4524; 15792</t>
+          <t>1745; 8223</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>607; 8126</t>
+          <t>607; 7356</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18877; 33773</t>
+          <t>19582; 33734</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8591; 23664</t>
+          <t>7312; 19839</t>
         </is>
       </c>
     </row>
@@ -2511,27 +2511,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26674</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>102596</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>84349</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>26007</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>85794</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26674</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>102596</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>191298</t>
+          <t>160513</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18811; 36281</t>
+          <t>19061; 37183</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73572; 100484</t>
+          <t>88182; 119994</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72427; 112454</t>
+          <t>68298; 100784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19669; 36274</t>
+          <t>18356; 35590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86351; 117902</t>
+          <t>72842; 100512</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81579; 123317</t>
+          <t>63892; 90549</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41958; 65636</t>
+          <t>41186; 64975</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>168896; 208998</t>
+          <t>168100; 210011</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166358; 223191</t>
+          <t>140977; 184591</t>
         </is>
       </c>
     </row>
